--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -33266,7 +33266,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
         <v>931</v>
       </c>
@@ -33282,10 +33282,10 @@
         <v>74</v>
       </c>
       <c r="G293" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H293" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I293" t="s" s="2">
         <v>73</v>
@@ -33688,7 +33688,7 @@
         <v>74</v>
       </c>
       <c r="G297" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H297" t="s" s="2">
         <v>73</v>
@@ -33774,7 +33774,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
         <v>946</v>
       </c>
@@ -33793,7 +33793,7 @@
         <v>80</v>
       </c>
       <c r="H298" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I298" t="s" s="2">
         <v>73</v>
@@ -33892,7 +33892,7 @@
         <v>74</v>
       </c>
       <c r="G299" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H299" t="s" s="2">
         <v>73</v>
@@ -33996,7 +33996,7 @@
         <v>74</v>
       </c>
       <c r="G300" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H300" t="s" s="2">
         <v>73</v>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
